--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/LOUISIANA_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/LOUISIANA_2017.xlsx
@@ -481,7 +481,7 @@
         <v>3</v>
       </c>
       <c r="D7">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="8">
@@ -517,7 +517,7 @@
         <v>3</v>
       </c>
       <c r="D9">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="10">
@@ -553,7 +553,7 @@
         <v>3</v>
       </c>
       <c r="D11">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="12">
@@ -715,7 +715,7 @@
         <v>3</v>
       </c>
       <c r="D20">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="21">
@@ -1021,7 +1021,7 @@
         <v>3</v>
       </c>
       <c r="D37">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="38">
@@ -1057,7 +1057,7 @@
         <v>3</v>
       </c>
       <c r="D39">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="40">
@@ -1129,7 +1129,7 @@
         <v>3</v>
       </c>
       <c r="D43">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="44">
@@ -1183,7 +1183,7 @@
         <v>3</v>
       </c>
       <c r="D46">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="47">
@@ -1237,7 +1237,7 @@
         <v>3</v>
       </c>
       <c r="D49">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="50">
@@ -1345,7 +1345,7 @@
         <v>3</v>
       </c>
       <c r="D55">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="56">
@@ -1435,7 +1435,7 @@
         <v>3</v>
       </c>
       <c r="D60">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="61">
@@ -1489,7 +1489,7 @@
         <v>3</v>
       </c>
       <c r="D63">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="64">
@@ -1831,7 +1831,7 @@
         <v>3</v>
       </c>
       <c r="D82">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="83">
@@ -2029,7 +2029,7 @@
         <v>3</v>
       </c>
       <c r="D93">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="94">
@@ -2083,7 +2083,7 @@
         <v>3</v>
       </c>
       <c r="D96">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="97">
@@ -2101,7 +2101,7 @@
         <v>3</v>
       </c>
       <c r="D97">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="98">
@@ -2173,7 +2173,7 @@
         <v>3</v>
       </c>
       <c r="D101">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="102">
@@ -2515,7 +2515,7 @@
         <v>3</v>
       </c>
       <c r="D120">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="121">
@@ -2551,7 +2551,7 @@
         <v>3</v>
       </c>
       <c r="D122">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="123">
@@ -2641,7 +2641,7 @@
         <v>3</v>
       </c>
       <c r="D127">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="128">
@@ -2731,7 +2731,7 @@
         <v>3</v>
       </c>
       <c r="D132">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="133">
@@ -2767,7 +2767,7 @@
         <v>3</v>
       </c>
       <c r="D134">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="135">
@@ -3001,7 +3001,7 @@
         <v>3</v>
       </c>
       <c r="D147">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="148">
@@ -3757,7 +3757,7 @@
         <v>3</v>
       </c>
       <c r="D189">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="190">
@@ -3793,7 +3793,7 @@
         <v>3</v>
       </c>
       <c r="D191">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="192">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C192">
@@ -4189,7 +4189,7 @@
         <v>3</v>
       </c>
       <c r="D213">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="214">
@@ -4351,7 +4351,7 @@
         <v>3</v>
       </c>
       <c r="D222">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="223">
@@ -4441,7 +4441,7 @@
         <v>3</v>
       </c>
       <c r="D227">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="228">
@@ -4909,7 +4909,7 @@
         <v>3</v>
       </c>
       <c r="D253">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="254">
@@ -4981,7 +4981,7 @@
         <v>3</v>
       </c>
       <c r="D257">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="258">
@@ -5053,7 +5053,7 @@
         <v>3</v>
       </c>
       <c r="D261">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="262">
@@ -5323,7 +5323,7 @@
         <v>3</v>
       </c>
       <c r="D276">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="277">
@@ -5359,7 +5359,7 @@
         <v>3</v>
       </c>
       <c r="D278">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="279">
@@ -5377,7 +5377,7 @@
         <v>3</v>
       </c>
       <c r="D279">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="280">
@@ -5413,7 +5413,7 @@
         <v>3</v>
       </c>
       <c r="D281">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="282">
@@ -5503,7 +5503,7 @@
         <v>3</v>
       </c>
       <c r="D286">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="287">
@@ -5539,7 +5539,7 @@
         <v>3</v>
       </c>
       <c r="D288">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="289">
@@ -5557,7 +5557,7 @@
         <v>3</v>
       </c>
       <c r="D289">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="290">
@@ -5701,7 +5701,7 @@
         <v>3</v>
       </c>
       <c r="D297">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="298">
@@ -6169,7 +6169,7 @@
         <v>3</v>
       </c>
       <c r="D323">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="324">
@@ -6223,7 +6223,7 @@
         <v>3</v>
       </c>
       <c r="D326">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="327">
@@ -6331,7 +6331,7 @@
         <v>3</v>
       </c>
       <c r="D332">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="333">
@@ -6367,7 +6367,7 @@
         <v>3</v>
       </c>
       <c r="D334">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="335">
@@ -6583,7 +6583,7 @@
         <v>3</v>
       </c>
       <c r="D346">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="347">
@@ -6637,7 +6637,7 @@
         <v>3</v>
       </c>
       <c r="D349">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="350">
@@ -6655,7 +6655,7 @@
         <v>3</v>
       </c>
       <c r="D350">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="351">
@@ -6871,7 +6871,7 @@
         <v>3</v>
       </c>
       <c r="D362">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="363">
@@ -6997,7 +6997,7 @@
         <v>3</v>
       </c>
       <c r="D369">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="370">
@@ -7015,7 +7015,7 @@
         <v>3</v>
       </c>
       <c r="D370">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="371">
@@ -7087,7 +7087,7 @@
         <v>3</v>
       </c>
       <c r="D374">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="375">
@@ -7789,7 +7789,7 @@
         <v>3</v>
       </c>
       <c r="D413">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="414">
@@ -8041,7 +8041,7 @@
         <v>3</v>
       </c>
       <c r="D427">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="428">
@@ -8221,7 +8221,7 @@
         <v>3</v>
       </c>
       <c r="D437">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="438">
@@ -8491,7 +8491,7 @@
         <v>3</v>
       </c>
       <c r="D452">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="453">
@@ -8563,7 +8563,7 @@
         <v>3</v>
       </c>
       <c r="D456">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="457">
@@ -8653,7 +8653,7 @@
         <v>3</v>
       </c>
       <c r="D461">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="462">
@@ -9175,7 +9175,7 @@
         <v>3</v>
       </c>
       <c r="D490">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="491">
@@ -9211,7 +9211,7 @@
         <v>3</v>
       </c>
       <c r="D492">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="493">
@@ -9409,7 +9409,7 @@
         <v>3</v>
       </c>
       <c r="D503">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="504">
@@ -9625,7 +9625,7 @@
         <v>3</v>
       </c>
       <c r="D515">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="516">
@@ -9661,7 +9661,7 @@
         <v>3</v>
       </c>
       <c r="D517">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="518">
@@ -10075,7 +10075,7 @@
         <v>3</v>
       </c>
       <c r="D540">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="541">
@@ -10111,7 +10111,7 @@
         <v>3</v>
       </c>
       <c r="D542">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="543">
@@ -10165,7 +10165,7 @@
         <v>3</v>
       </c>
       <c r="D545">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="546">
@@ -10417,7 +10417,7 @@
         <v>3</v>
       </c>
       <c r="D559">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="560">
@@ -10489,7 +10489,7 @@
         <v>3</v>
       </c>
       <c r="D563">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="564">
@@ -10597,7 +10597,7 @@
         <v>3</v>
       </c>
       <c r="D569">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="570">
@@ -10669,7 +10669,7 @@
         <v>3</v>
       </c>
       <c r="D573">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="574">
@@ -10759,7 +10759,7 @@
         <v>3</v>
       </c>
       <c r="D578">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="579">
@@ -10867,7 +10867,7 @@
         <v>3</v>
       </c>
       <c r="D584">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="585">
@@ -11011,7 +11011,7 @@
         <v>3</v>
       </c>
       <c r="D592">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="593">
@@ -11191,7 +11191,7 @@
         <v>3</v>
       </c>
       <c r="D602">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="603">
@@ -11281,7 +11281,7 @@
         <v>3</v>
       </c>
       <c r="D607">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="608">
@@ -11389,7 +11389,7 @@
         <v>3</v>
       </c>
       <c r="D613">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="614">
@@ -11407,7 +11407,7 @@
         <v>3</v>
       </c>
       <c r="D614">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="615">
@@ -11587,7 +11587,7 @@
         <v>3</v>
       </c>
       <c r="D624">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="625">
@@ -11659,7 +11659,7 @@
         <v>3</v>
       </c>
       <c r="D628">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="629">
@@ -11803,7 +11803,7 @@
         <v>3</v>
       </c>
       <c r="D636">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="637">
@@ -11875,7 +11875,7 @@
         <v>3</v>
       </c>
       <c r="D640">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="641">
@@ -12001,7 +12001,7 @@
         <v>3</v>
       </c>
       <c r="D647">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="648">
@@ -12091,7 +12091,7 @@
         <v>3</v>
       </c>
       <c r="D652">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="653">
@@ -12145,7 +12145,7 @@
         <v>3</v>
       </c>
       <c r="D655">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="656">
@@ -12307,7 +12307,7 @@
         <v>3</v>
       </c>
       <c r="D664">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="665">
@@ -12415,7 +12415,7 @@
         <v>3</v>
       </c>
       <c r="D670">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="671">
@@ -12595,7 +12595,7 @@
         <v>3</v>
       </c>
       <c r="D680">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="681">
@@ -12649,7 +12649,7 @@
         <v>3</v>
       </c>
       <c r="D683">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="684">
@@ -12883,7 +12883,7 @@
         <v>3</v>
       </c>
       <c r="D696">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="697">
@@ -13153,7 +13153,7 @@
         <v>3</v>
       </c>
       <c r="D711">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="712">
@@ -13225,7 +13225,7 @@
         <v>3</v>
       </c>
       <c r="D715">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="716">
@@ -13765,7 +13765,7 @@
         <v>3</v>
       </c>
       <c r="D745">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="746">
@@ -13981,7 +13981,7 @@
         <v>3</v>
       </c>
       <c r="D757">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="758">
@@ -14017,7 +14017,7 @@
         <v>3</v>
       </c>
       <c r="D759">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="760">
@@ -14053,7 +14053,7 @@
         <v>3</v>
       </c>
       <c r="D761">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="762">
@@ -14215,7 +14215,7 @@
         <v>3</v>
       </c>
       <c r="D770">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="771">
@@ -14323,7 +14323,7 @@
         <v>3</v>
       </c>
       <c r="D776">
-        <v>0.0009445843828715365</v>
+        <v>0.0009445843828715364</v>
       </c>
     </row>
     <row r="777">
